--- a/data/dados_cerveja.xlsx
+++ b/data/dados_cerveja.xlsx
@@ -11,22 +11,58 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="15">
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>cerveja</t>
-  </si>
-  <si>
-    <t>nota</t>
+    <t>temperatura</t>
+  </si>
+  <si>
+    <t>copo</t>
+  </si>
+  <si>
+    <t>espuma</t>
+  </si>
+  <si>
+    <t>cor</t>
+  </si>
+  <si>
+    <t>classe</t>
+  </si>
+  <si>
+    <t>mud</t>
+  </si>
+  <si>
+    <t>não</t>
+  </si>
+  <si>
+    <t>escura</t>
+  </si>
+  <si>
+    <t>weissbier</t>
+  </si>
+  <si>
+    <t>sim</t>
+  </si>
+  <si>
+    <t>pint</t>
+  </si>
+  <si>
+    <t>clara</t>
+  </si>
+  <si>
+    <t>pale-ale</t>
+  </si>
+  <si>
+    <t>pilsen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -34,6 +70,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -53,13 +101,17 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -287,170 +339,255 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>1.0</v>
       </c>
-      <c r="B2" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0.75</v>
+      <c r="B2" s="2">
+        <v>-5.0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>2.0</v>
       </c>
-      <c r="B3" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="B3" s="2">
+        <v>-5.0</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
         <v>3.0</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C4" s="1">
-        <v>1.75</v>
+      <c r="B4" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>4.0</v>
       </c>
-      <c r="B5" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1.75</v>
+      <c r="B5" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>5.0</v>
       </c>
-      <c r="B6" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C6" s="1">
-        <v>4.2</v>
+      <c r="B6" s="2">
+        <v>-5.0</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>6.0</v>
       </c>
-      <c r="B7" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C7" s="1">
-        <v>6.5</v>
+      <c r="B7" s="2">
+        <v>-5.0</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>7.0</v>
       </c>
-      <c r="B8" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C8" s="1">
-        <v>2.9</v>
+      <c r="B8" s="2">
+        <v>-5.0</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1">
+      <c r="A9" s="2">
         <v>8.0</v>
       </c>
-      <c r="B9" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C9" s="1">
-        <v>6.2</v>
-      </c>
+      <c r="B9" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="3"/>
     </row>
     <row r="10">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
         <v>9.0</v>
       </c>
-      <c r="B10" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C10" s="1">
-        <v>7.0</v>
+      <c r="B10" s="2">
+        <v>-5.0</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1">
+      <c r="A11" s="2">
         <v>10.0</v>
       </c>
-      <c r="B11" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C11" s="1">
-        <v>6.2</v>
+      <c r="B11" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1">
+      <c r="A12" s="2">
         <v>11.0</v>
       </c>
-      <c r="B12" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C12" s="1">
-        <v>8.5</v>
+      <c r="B12" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1">
+      <c r="A13" s="2">
         <v>12.0</v>
       </c>
-      <c r="B13" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C13" s="1">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="B14" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C14" s="1">
-        <v>8.6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="B15" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C15" s="1">
-        <v>9.9</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="B16" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C16" s="1">
-        <v>10.0</v>
+      <c r="B13" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
